--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4894,17 +4894,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13210,17 +13210,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13606,17 +13606,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G130" t="n">

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.68</v>
+        <v>7.6</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="N97" t="n">
-        <v>4.7</v>
+        <v>1.39</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13342,17 +13342,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.5</v>
+        <v>1.68</v>
       </c>
       <c r="M98" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>1.87</v>
+        <v>4.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13738,17 +13738,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13342,17 +13342,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.68</v>
+        <v>3.5</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N98" t="n">
-        <v>4.7</v>
+        <v>1.87</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13474,17 +13474,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.5</v>
+        <v>1.68</v>
       </c>
       <c r="M99" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>1.87</v>
+        <v>4.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G130" t="n">

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL130"/>
+  <dimension ref="A1:AL129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.25</v>
+        <v>1.35</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="N46" t="n">
-        <v>2.2</v>
+        <v>9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13342,17 +13342,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.5</v>
+        <v>1.68</v>
       </c>
       <c r="M98" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>1.87</v>
+        <v>4.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13474,17 +13474,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.68</v>
+        <v>3.5</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N99" t="n">
-        <v>4.7</v>
+        <v>1.87</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,16 +14054,16 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,16 +14186,16 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF104" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>45884.91666666666</v>
+        <v>45884.875</v>
       </c>
     </row>
     <row r="129">
@@ -17520,138 +17520,6 @@
         </is>
       </c>
       <c r="AL129" s="3" t="n">
-        <v>45884.95833333334</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Colorado Rapids II</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Austin II</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" t="n">
-        <v>0</v>
-      </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL130" s="3" t="n">
         <v>45884.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL129"/>
+  <dimension ref="A1:AL131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="M53" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="N53" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
         <v>1.8</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7629,27 +7629,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="AL55" s="3" t="n">
-        <v>45884.58333333334</v>
+        <v>45884.57291666666</v>
       </c>
     </row>
     <row r="56">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8120,10 +8120,10 @@
         <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -8157,12 +8157,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="AL59" s="3" t="n">
-        <v>45884.60416666666</v>
+        <v>45884.58333333334</v>
       </c>
     </row>
     <row r="60">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13210,17 +13210,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="M97" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="N97" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13474,17 +13474,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="M99" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="N99" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,16 +14054,16 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF103" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,16 +14186,16 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
         <v>0</v>
@@ -14229,12 +14229,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="AL105" s="3" t="n">
-        <v>45884.6875</v>
+        <v>45884.66666666666</v>
       </c>
     </row>
     <row r="106">
@@ -14361,27 +14361,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="AL106" s="3" t="n">
-        <v>45884.70833333334</v>
+        <v>45884.6875</v>
       </c>
     </row>
     <row r="107">
@@ -14493,12 +14493,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14616,7 +14616,7 @@
         </is>
       </c>
       <c r="AL107" s="3" t="n">
-        <v>45884.75</v>
+        <v>45884.70833333334</v>
       </c>
     </row>
     <row r="108">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="AL108" s="3" t="n">
-        <v>45884.79166666666</v>
+        <v>45884.75</v>
       </c>
     </row>
     <row r="109">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>45884.875</v>
+        <v>45884.88194444445</v>
       </c>
     </row>
     <row r="129">
@@ -17397,129 +17397,393 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Deportivo Maipú</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL129" s="3" t="n">
+        <v>45884.91666666666</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL129" s="3" t="n">
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL130" s="3" t="n">
+        <v>45884.95833333334</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL131" s="3" t="n">
         <v>45884.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL131"/>
+  <dimension ref="A1:AL129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1466,40 +1466,40 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1508,34 +1508,34 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45884.41666666666</v>
+        <v>45884.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45884.41666666666</v>
+        <v>45884.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2745,27 +2745,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45884.41666666666</v>
+        <v>45884.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45884.41666666666</v>
+        <v>45884.5</v>
       </c>
     </row>
     <row r="20">
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45884.41666666666</v>
+        <v>45884.5</v>
       </c>
     </row>
     <row r="21">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45884.45833333334</v>
+        <v>45884.5</v>
       </c>
     </row>
     <row r="22">
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,70 +3314,70 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45884.45833333334</v>
+        <v>45884.5</v>
       </c>
     </row>
     <row r="23">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45884.45833333334</v>
+        <v>45884.5</v>
       </c>
     </row>
     <row r="24">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,40 +4238,40 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45884.5</v>
+        <v>45884.52083333334</v>
       </c>
     </row>
     <row r="35">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45884.5</v>
+        <v>45884.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45884.5</v>
+        <v>45884.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5348,10 +5348,10 @@
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45884.5</v>
+        <v>45884.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45884.52083333334</v>
+        <v>45884.54166666666</v>
       </c>
     </row>
     <row r="39">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="N39" t="n">
-        <v>2.37</v>
+        <v>3.78</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45884.52083333334</v>
+        <v>45884.54166666666</v>
       </c>
     </row>
     <row r="40">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,16 +6530,16 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="N49" t="n">
-        <v>2.2</v>
+        <v>8.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7064,10 +7064,10 @@
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7101,27 +7101,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>45884.54166666666</v>
+        <v>45884.5625</v>
       </c>
     </row>
     <row r="52">
@@ -7233,27 +7233,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.91</v>
+        <v>3.55</v>
       </c>
       <c r="M52" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45884.54166666666</v>
+        <v>45884.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -7365,27 +7365,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.35</v>
+        <v>2.32</v>
       </c>
       <c r="M53" t="n">
-        <v>4.9</v>
+        <v>3.03</v>
       </c>
       <c r="N53" t="n">
-        <v>9</v>
+        <v>2.79</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>45884.54166666666</v>
+        <v>45884.58333333334</v>
       </c>
     </row>
     <row r="54">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,16 +7586,16 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="AL54" s="3" t="n">
-        <v>45884.5625</v>
+        <v>45884.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="AL55" s="3" t="n">
-        <v>45884.57291666666</v>
+        <v>45884.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -7761,27 +7761,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="AL56" s="3" t="n">
-        <v>45884.58333333334</v>
+        <v>45884.60416666666</v>
       </c>
     </row>
     <row r="57">
@@ -7893,27 +7893,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="AL57" s="3" t="n">
-        <v>45884.58333333334</v>
+        <v>45884.60416666666</v>
       </c>
     </row>
     <row r="58">
@@ -8025,27 +8025,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8120,10 +8120,10 @@
         <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AL58" s="3" t="n">
-        <v>45884.58333333334</v>
+        <v>45884.60416666666</v>
       </c>
     </row>
     <row r="59">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="AL59" s="3" t="n">
-        <v>45884.58333333334</v>
+        <v>45884.60416666666</v>
       </c>
     </row>
     <row r="60">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="AL67" s="3" t="n">
-        <v>45884.60416666666</v>
+        <v>45884.61458333334</v>
       </c>
     </row>
     <row r="68">
@@ -9345,27 +9345,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9428,16 +9428,16 @@
         <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>45884.60416666666</v>
+        <v>45884.62152777778</v>
       </c>
     </row>
     <row r="69">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>45884.60416666666</v>
+        <v>45884.625</v>
       </c>
     </row>
     <row r="70">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>45884.60416666666</v>
+        <v>45884.625</v>
       </c>
     </row>
     <row r="71">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="AL71" s="3" t="n">
-        <v>45884.61458333334</v>
+        <v>45884.625</v>
       </c>
     </row>
     <row r="72">
@@ -9873,27 +9873,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9956,16 +9956,16 @@
         <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AL72" s="3" t="n">
-        <v>45884.62152777778</v>
+        <v>45884.625</v>
       </c>
     </row>
     <row r="73">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11816,10 +11816,10 @@
         <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11853,12 +11853,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>45884.625</v>
+        <v>45884.63541666666</v>
       </c>
     </row>
     <row r="88">
@@ -11985,12 +11985,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>45884.625</v>
+        <v>45884.63541666666</v>
       </c>
     </row>
     <row r="89">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12249,12 +12249,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="AL90" s="3" t="n">
-        <v>45884.63541666666</v>
+        <v>45884.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="AL91" s="3" t="n">
-        <v>45884.63541666666</v>
+        <v>45884.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12909,12 +12909,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="AL95" s="3" t="n">
-        <v>45884.64583333334</v>
+        <v>45884.65625</v>
       </c>
     </row>
     <row r="96">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13078,17 +13078,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="AL96" s="3" t="n">
-        <v>45884.64583333334</v>
+        <v>45884.65625</v>
       </c>
     </row>
     <row r="97">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="M97" t="n">
-        <v>3.9</v>
+        <v>3.57</v>
       </c>
       <c r="N97" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13474,17 +13474,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,16 +13790,16 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF101" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45884.65625</v>
+        <v>45884.66666666666</v>
       </c>
     </row>
     <row r="102">
@@ -13833,27 +13833,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45884.65625</v>
+        <v>45884.66666666666</v>
       </c>
     </row>
     <row r="103">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,16 +14054,16 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
         <v>0</v>
@@ -14097,27 +14097,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>45884.66666666666</v>
+        <v>45884.6875</v>
       </c>
     </row>
     <row r="105">
@@ -14229,27 +14229,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="AL105" s="3" t="n">
-        <v>45884.66666666666</v>
+        <v>45884.70833333334</v>
       </c>
     </row>
     <row r="106">
@@ -14361,27 +14361,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="AL106" s="3" t="n">
-        <v>45884.6875</v>
+        <v>45884.75</v>
       </c>
     </row>
     <row r="107">
@@ -14493,12 +14493,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14616,7 +14616,7 @@
         </is>
       </c>
       <c r="AL107" s="3" t="n">
-        <v>45884.70833333334</v>
+        <v>45884.79166666666</v>
       </c>
     </row>
     <row r="108">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="AL108" s="3" t="n">
-        <v>45884.75</v>
+        <v>45884.79166666666</v>
       </c>
     </row>
     <row r="109">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15945,12 +15945,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="AL118" s="3" t="n">
-        <v>45884.79166666666</v>
+        <v>45884.83333333334</v>
       </c>
     </row>
     <row r="119">
@@ -16077,12 +16077,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16160,16 +16160,16 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="AL119" s="3" t="n">
-        <v>45884.79166666666</v>
+        <v>45884.83333333334</v>
       </c>
     </row>
     <row r="120">
@@ -16209,12 +16209,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16332,7 +16332,7 @@
         </is>
       </c>
       <c r="AL120" s="3" t="n">
-        <v>45884.83333333334</v>
+        <v>45884.85416666666</v>
       </c>
     </row>
     <row r="121">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16464,7 +16464,7 @@
         </is>
       </c>
       <c r="AL121" s="3" t="n">
-        <v>45884.83333333334</v>
+        <v>45884.875</v>
       </c>
     </row>
     <row r="122">
@@ -16473,12 +16473,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16596,7 +16596,7 @@
         </is>
       </c>
       <c r="AL122" s="3" t="n">
-        <v>45884.85416666666</v>
+        <v>45884.875</v>
       </c>
     </row>
     <row r="123">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17001,12 +17001,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17084,10 +17084,10 @@
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB126" t="n">
         <v>0</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="AL126" s="3" t="n">
-        <v>45884.875</v>
+        <v>45884.88194444445</v>
       </c>
     </row>
     <row r="127">
@@ -17133,12 +17133,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17256,7 +17256,7 @@
         </is>
       </c>
       <c r="AL127" s="3" t="n">
-        <v>45884.875</v>
+        <v>45884.91666666666</v>
       </c>
     </row>
     <row r="128">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>45884.88194444445</v>
+        <v>45884.95833333334</v>
       </c>
     </row>
     <row r="129">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17520,270 +17520,6 @@
         </is>
       </c>
       <c r="AL129" s="3" t="n">
-        <v>45884.91666666666</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" t="n">
-        <v>0</v>
-      </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL130" s="3" t="n">
-        <v>45884.95833333334</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Colorado Rapids II</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Austin II</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" t="n">
-        <v>0</v>
-      </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL131" s="3" t="n">
         <v>45884.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL129"/>
+  <dimension ref="A1:AL130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.42</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V4" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.08</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.23</v>
+        <v>3.69</v>
       </c>
       <c r="M6" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.21</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>2.54</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="U6" t="n">
         <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="n">
         <v>7.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.69</v>
+        <v>2.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
-        <v>4.6</v>
+        <v>3.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.54</v>
+        <v>3.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
         <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="n">
         <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2877,27 +2877,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45884.5</v>
+        <v>45884.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,70 +3314,70 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,70 +3710,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>3.38</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.32</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,40 +4238,40 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,40 +4766,40 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4826,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45884.52083333334</v>
+        <v>45884.5</v>
       </c>
     </row>
     <row r="35">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5348,10 +5348,10 @@
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45884.54166666666</v>
+        <v>45884.52083333334</v>
       </c>
     </row>
     <row r="38">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.66</v>
+        <v>3.47</v>
       </c>
       <c r="M38" t="n">
         <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.67</v>
+        <v>3.32</v>
       </c>
       <c r="M39" t="n">
-        <v>3.92</v>
+        <v>3.66</v>
       </c>
       <c r="N39" t="n">
-        <v>3.78</v>
+        <v>1.83</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,16 +5606,16 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,16 +6530,16 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>3.02</v>
       </c>
       <c r="M48" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N48" t="n">
-        <v>3.03</v>
+        <v>2.21</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.27</v>
+        <v>2.11</v>
       </c>
       <c r="M49" t="n">
-        <v>4.5</v>
+        <v>3.78</v>
       </c>
       <c r="N49" t="n">
-        <v>8.9</v>
+        <v>2.63</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.11</v>
+        <v>1.27</v>
       </c>
       <c r="M50" t="n">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="N50" t="n">
-        <v>2.63</v>
+        <v>8.9</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,16 +7058,16 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7101,27 +7101,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>45884.5625</v>
+        <v>45884.54166666666</v>
       </c>
     </row>
     <row r="52">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45884.58333333334</v>
+        <v>45884.5625</v>
       </c>
     </row>
     <row r="53">
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7547,43 +7547,43 @@
         <v>1.3</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AB54" t="n">
         <v>1.3</v>
@@ -7598,16 +7598,16 @@
         <v>1.93</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7761,27 +7761,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q56" t="n">
         <v>2.6</v>
       </c>
-      <c r="M56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="AL56" s="3" t="n">
-        <v>45884.60416666666</v>
+        <v>45884.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8108,10 +8108,10 @@
         <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="M59" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N59" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.73</v>
+        <v>2.28</v>
       </c>
       <c r="M64" t="n">
-        <v>3.59</v>
+        <v>2.95</v>
       </c>
       <c r="N64" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="AL67" s="3" t="n">
-        <v>45884.61458333334</v>
+        <v>45884.60416666666</v>
       </c>
     </row>
     <row r="68">
@@ -9345,27 +9345,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9428,16 +9428,16 @@
         <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>45884.62152777778</v>
+        <v>45884.61458333334</v>
       </c>
     </row>
     <row r="69">
@@ -9477,27 +9477,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.4</v>
+        <v>1.55</v>
       </c>
       <c r="M69" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9560,16 +9560,16 @@
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>45884.625</v>
+        <v>45884.62152777778</v>
       </c>
     </row>
     <row r="70">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="M71" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="N71" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="N76" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>2.51</v>
+        <v>3.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N83" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,16 +11414,16 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="M86" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="N86" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD86" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11853,12 +11853,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="M87" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>45884.63541666666</v>
+        <v>45884.625</v>
       </c>
     </row>
     <row r="88">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="M88" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N89" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12249,12 +12249,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="AL90" s="3" t="n">
-        <v>45884.64583333334</v>
+        <v>45884.63541666666</v>
       </c>
     </row>
     <row r="91">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="M94" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12909,12 +12909,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="AL95" s="3" t="n">
-        <v>45884.65625</v>
+        <v>45884.64583333334</v>
       </c>
     </row>
     <row r="96">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13078,17 +13078,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>7.6</v>
+        <v>3.41</v>
       </c>
       <c r="M96" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="N96" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13342,17 +13342,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13606,17 +13606,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13738,17 +13738,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="M101" t="n">
-        <v>5.6</v>
+        <v>4.33</v>
       </c>
       <c r="N101" t="n">
-        <v>8</v>
+        <v>1.39</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,16 +13790,16 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45884.66666666666</v>
+        <v>45884.65625</v>
       </c>
     </row>
     <row r="102">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,16 +14186,16 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF104" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>45884.6875</v>
+        <v>45884.66666666666</v>
       </c>
     </row>
     <row r="105">
@@ -14229,27 +14229,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="AL105" s="3" t="n">
-        <v>45884.70833333334</v>
+        <v>45884.6875</v>
       </c>
     </row>
     <row r="106">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="AL106" s="3" t="n">
-        <v>45884.75</v>
+        <v>45884.70833333334</v>
       </c>
     </row>
     <row r="107">
@@ -14493,12 +14493,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14616,7 +14616,7 @@
         </is>
       </c>
       <c r="AL107" s="3" t="n">
-        <v>45884.79166666666</v>
+        <v>45884.75</v>
       </c>
     </row>
     <row r="108">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15945,12 +15945,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="AL118" s="3" t="n">
-        <v>45884.83333333334</v>
+        <v>45884.79166666666</v>
       </c>
     </row>
     <row r="119">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16160,16 +16160,16 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16209,12 +16209,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="M120" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="N120" t="n">
-        <v>3.55</v>
+        <v>2.52</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16292,16 +16292,16 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16332,7 +16332,7 @@
         </is>
       </c>
       <c r="AL120" s="3" t="n">
-        <v>45884.85416666666</v>
+        <v>45884.83333333334</v>
       </c>
     </row>
     <row r="121">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         </is>
       </c>
       <c r="AL121" s="3" t="n">
-        <v>45884.875</v>
+        <v>45884.85416666666</v>
       </c>
     </row>
     <row r="122">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17001,12 +17001,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="M126" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N126" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17084,16 +17084,16 @@
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="AL126" s="3" t="n">
-        <v>45884.88194444445</v>
+        <v>45884.875</v>
       </c>
     </row>
     <row r="127">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17216,10 +17216,10 @@
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB127" t="n">
         <v>0</v>
@@ -17256,7 +17256,7 @@
         </is>
       </c>
       <c r="AL127" s="3" t="n">
-        <v>45884.91666666666</v>
+        <v>45884.88194444445</v>
       </c>
     </row>
     <row r="128">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>45884.95833333334</v>
+        <v>45884.91666666666</v>
       </c>
     </row>
     <row r="129">
@@ -17402,124 +17402,256 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL129" s="3" t="n">
+        <v>45884.95833333334</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L129" t="n">
+      <c r="L130" t="n">
         <v>2.39</v>
       </c>
-      <c r="M129" t="n">
+      <c r="M130" t="n">
         <v>3.45</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N130" t="n">
         <v>2.44</v>
       </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC129" t="n">
+      <c r="AC130" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL129" s="3" t="n">
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL130" s="3" t="n">
         <v>45884.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.69</v>
+        <v>2.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>3.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.54</v>
+        <v>3.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="n">
         <v>7.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.23</v>
+        <v>3.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.21</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.58</v>
+        <v>2.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE7" t="n">
         <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
         <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.95</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="M25" t="n">
-        <v>2.81</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
-        <v>3.09</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>2.49</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.34</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.57</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.25</v>
-      </c>
       <c r="V25" t="n">
-        <v>9.85</v>
+        <v>4.8</v>
       </c>
       <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.03</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y25" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.39</v>
+        <v>4.79</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>2.51</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,70 +3842,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O26" t="n">
         <v>3.09</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,40 +4766,40 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4826,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.47</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N38" t="n">
-        <v>1.83</v>
+        <v>3.03</v>
       </c>
       <c r="O38" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC38" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,16 +5606,16 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="M43" t="n">
-        <v>3.92</v>
+        <v>2.98</v>
       </c>
       <c r="N43" t="n">
-        <v>3.78</v>
+        <v>2.21</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>3.32</v>
       </c>
       <c r="M47" t="n">
-        <v>3.08</v>
+        <v>3.66</v>
       </c>
       <c r="N47" t="n">
-        <v>3.03</v>
+        <v>1.83</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,16 +6662,16 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,40 +6746,40 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.02</v>
+        <v>3.47</v>
       </c>
       <c r="M48" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="O48" t="n">
-        <v>3.34</v>
+        <v>3.93</v>
       </c>
       <c r="P48" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.93</v>
+        <v>2.61</v>
       </c>
       <c r="R48" t="n">
         <v>1.32</v>
       </c>
       <c r="S48" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T48" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="U48" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V48" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W48" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
         <v>1.01</v>
@@ -6794,10 +6794,10 @@
         <v>4</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
         <v>2.88</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="M55" t="n">
-        <v>3.03</v>
+        <v>3.36</v>
       </c>
       <c r="N55" t="n">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="O55" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="R55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE55" t="n">
         <v>1.4</v>
       </c>
-      <c r="S55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V55" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF55" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH55" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD56" t="n">
         <v>3.55</v>
       </c>
-      <c r="M56" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O56" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3</v>
-      </c>
       <c r="AE56" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH56" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="M58" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N58" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8108,10 +8108,10 @@
         <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9164,10 +9164,10 @@
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.67</v>
+        <v>2.82</v>
       </c>
       <c r="M71" t="n">
-        <v>3.51</v>
+        <v>3.01</v>
       </c>
       <c r="N71" t="n">
-        <v>4.3</v>
+        <v>2.31</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="M76" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.83</v>
+        <v>5.4</v>
       </c>
       <c r="M78" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="N78" t="n">
-        <v>3.7</v>
+        <v>1.55</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.9</v>
+        <v>1.19</v>
       </c>
       <c r="M79" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N79" t="n">
-        <v>2.25</v>
+        <v>11</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N87" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="M88" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="N88" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="M90" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="N90" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="M93" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13210,17 +13210,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.64</v>
+        <v>1.68</v>
       </c>
       <c r="M97" t="n">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>1.77</v>
+        <v>4.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13606,17 +13606,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.68</v>
+        <v>3.41</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="N100" t="n">
-        <v>4.7</v>
+        <v>1.98</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,16 +13922,16 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF102" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,16 +14186,16 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
         <v>0</v>
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45884.27083333334</v>
+        <v>45884.25</v>
       </c>
     </row>
     <row r="4">
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45884.29166666666</v>
+        <v>45884.27083333334</v>
       </c>
     </row>
     <row r="5">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>3.69</v>
       </c>
       <c r="M8" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O8" t="n">
         <v>4.6</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="P8" t="n">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.53</v>
+        <v>2.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AA8" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45884.35763888889</v>
+        <v>45884.29166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.95</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45884.375</v>
+        <v>45884.35763888889</v>
       </c>
     </row>
     <row r="10">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" t="n">
         <v>4.6</v>
       </c>
-      <c r="O10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.6</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45884.38541666666</v>
+        <v>45884.375</v>
       </c>
     </row>
     <row r="14">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45884.41666666666</v>
+        <v>45884.38541666666</v>
       </c>
     </row>
     <row r="15">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45884.45833333334</v>
+        <v>45884.41666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3970,44 +3970,44 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,40 +4634,40 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4694,10 +4694,10 @@
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="M42" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>3.78</v>
+        <v>3.32</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>2.98</v>
+        <v>3.69</v>
       </c>
       <c r="N43" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
-        <v>3.34</v>
+        <v>3.61</v>
       </c>
       <c r="P43" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="T43" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U43" t="n">
         <v>1.48</v>
       </c>
       <c r="V43" t="n">
-        <v>5.3</v>
+        <v>5.65</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AA43" t="n">
         <v>4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF43" t="n">
         <v>1.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.5</v>
+        <v>4.44</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>4.33</v>
+        <v>2.72</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="M45" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="O45" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.32</v>
+        <v>1.67</v>
       </c>
       <c r="M47" t="n">
-        <v>3.66</v>
+        <v>3.92</v>
       </c>
       <c r="N47" t="n">
-        <v>1.83</v>
+        <v>3.78</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,16 +6662,16 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="N48" t="n">
         <v>1.83</v>
       </c>
       <c r="O48" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.11</v>
+        <v>1.27</v>
       </c>
       <c r="M49" t="n">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="N49" t="n">
-        <v>2.63</v>
+        <v>8.9</v>
       </c>
       <c r="O49" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="M58" t="n">
-        <v>2.95</v>
+        <v>3.59</v>
       </c>
       <c r="N58" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8240,10 +8240,10 @@
         <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N65" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9164,10 +9164,10 @@
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="M67" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="N70" t="n">
-        <v>3.2</v>
+        <v>2.31</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="M71" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="N71" t="n">
-        <v>2.31</v>
+        <v>2.51</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="M73" t="n">
-        <v>2.93</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC73" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>1.61</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M75" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="N75" t="n">
-        <v>2.48</v>
+        <v>4.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="M78" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>1.55</v>
+        <v>3.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD83" t="n">
         <v>2.35</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="M87" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="M88" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="M89" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="N89" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC89" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="M90" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,76 +12422,76 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AI91" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13078,17 +13078,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13210,17 +13210,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.68</v>
+        <v>3.41</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="N97" t="n">
-        <v>4.7</v>
+        <v>1.98</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13606,17 +13606,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.41</v>
+        <v>1.68</v>
       </c>
       <c r="M100" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="N100" t="n">
-        <v>1.98</v>
+        <v>4.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AC100" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13738,17 +13738,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>7.6</v>
+        <v>3.64</v>
       </c>
       <c r="M101" t="n">
-        <v>4.33</v>
+        <v>3.57</v>
       </c>
       <c r="N101" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,16 +13922,16 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,16 +14054,16 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF103" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -683,13 +683,13 @@
         <v>1.7</v>
       </c>
       <c r="O2" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
@@ -1079,13 +1079,13 @@
         <v>2.38</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.42</v>
@@ -1211,13 +1211,13 @@
         <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>3.21</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>3.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>2.57</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA7" t="n">
         <v>3.3</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>2.19</v>
+        <v>8.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.53</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.38</v>
+        <v>1.94</v>
       </c>
       <c r="M21" t="n">
-        <v>3.09</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.32</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,40 +3578,40 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3638,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,70 +3842,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3970,44 +3970,44 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,70 +4238,70 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O38" t="n">
         <v>2.15</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="N39" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="O39" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>3.78</v>
       </c>
       <c r="O40" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.22</v>
+        <v>1.27</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.01</v>
+        <v>8.9</v>
       </c>
       <c r="O41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N42" t="n">
         <v>1.91</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.32</v>
-      </c>
       <c r="O42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="T42" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC42" t="n">
         <v>2.21</v>
       </c>
-      <c r="U42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AD42" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="N47" t="n">
-        <v>3.78</v>
+        <v>2.08</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6632,58 +6632,58 @@
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2</v>
+      </c>
+      <c r="P48" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q48" t="n">
         <v>1.83</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z49" t="n">
         <v>1.27</v>
       </c>
-      <c r="M49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N49" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7415,13 +7415,13 @@
         <v>1.3</v>
       </c>
       <c r="O53" t="n">
-        <v>6.3</v>
+        <v>3.32</v>
       </c>
       <c r="P53" t="n">
-        <v>2.89</v>
+        <v>33</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="R53" t="n">
         <v>1.14</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P54" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V54" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD54" t="n">
         <v>3.55</v>
       </c>
-      <c r="M54" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O54" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V54" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>3</v>
-      </c>
       <c r="AE54" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH54" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="M56" t="n">
-        <v>3.03</v>
+        <v>3.36</v>
       </c>
       <c r="N56" t="n">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="O56" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>10</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="R56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE56" t="n">
         <v>1.4</v>
       </c>
-      <c r="S56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF56" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH56" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8240,10 +8240,10 @@
         <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N60" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8372,16 +8372,16 @@
         <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,76 +9782,76 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="M71" t="n">
-        <v>2.93</v>
+        <v>4.4</v>
       </c>
       <c r="N71" t="n">
-        <v>2.51</v>
+        <v>6</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,76 +10046,76 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,58 +10442,58 @@
         </is>
       </c>
       <c r="L76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
         <v>2.1</v>
       </c>
-      <c r="M76" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AC76" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.8</v>
+        <v>1.21</v>
       </c>
       <c r="M78" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="N78" t="n">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10724,58 +10724,58 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB78" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC78" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC78" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,16 +11414,16 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="M84" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="N84" t="n">
-        <v>2.48</v>
+        <v>1.75</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11516,58 +11516,58 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB84" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG84" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC84" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>0</v>
-      </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.21</v>
+        <v>2.82</v>
       </c>
       <c r="M85" t="n">
-        <v>5.4</v>
+        <v>3.01</v>
       </c>
       <c r="N85" t="n">
-        <v>12</v>
+        <v>2.31</v>
       </c>
       <c r="O85" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC85" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC85" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="M87" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="N87" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="M88" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="N88" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="M89" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="N89" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC89" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>1.67</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="M90" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N90" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC90" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,76 +12422,76 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="M91" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O91" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12572,58 +12572,58 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13078,17 +13078,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>7.6</v>
+        <v>3.41</v>
       </c>
       <c r="M96" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="N96" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="M97" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="N97" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13342,80 +13342,80 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13474,80 +13474,80 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI99" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13606,17 +13606,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,76 +13874,76 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AI102" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,16 +14054,16 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14270,76 +14270,76 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AI105" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16160,16 +16160,16 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16292,16 +16292,16 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="M121" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N121" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="M127" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="N127" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17216,10 +17216,10 @@
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AB127" t="n">
         <v>0</v>
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,73 +1070,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="N5" t="n">
-        <v>2.57</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
         <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.38</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI5" t="n">
         <v>1.08</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="O6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.65</v>
       </c>
-      <c r="P6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.23</v>
+        <v>3.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE7" t="n">
         <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
         <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,70 +3974,70 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,70 +4106,70 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.12</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="R28" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>9.85</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4234,44 +4234,44 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45884.52083333334</v>
+        <v>45884.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.02</v>
+        <v>1.27</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.21</v>
+        <v>8.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="T34" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="U34" t="n">
         <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>5.95</v>
+        <v>5.55</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>13.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AF34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.55</v>
       </c>
-      <c r="AG34" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH34" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O35" t="n">
         <v>2.15</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V35" t="n">
         <v>5.8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>13.5</v>
+        <v>10.9</v>
       </c>
       <c r="Z35" t="n">
         <v>1.21</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="AE35" t="n">
         <v>1.4</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>5.06</v>
+        <v>5.3</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.27</v>
+        <v>2.11</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.78</v>
       </c>
       <c r="N36" t="n">
-        <v>8.9</v>
+        <v>2.63</v>
       </c>
       <c r="O36" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
       <c r="P36" t="n">
-        <v>13.75</v>
+        <v>18.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.75</v>
+        <v>2.03</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V36" t="n">
-        <v>5.55</v>
+        <v>4.65</v>
       </c>
       <c r="W36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.12</v>
       </c>
-      <c r="X36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AA36" t="n">
-        <v>3.94</v>
+        <v>5.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>1.67</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P40" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S40" t="n">
         <v>3.4</v>
       </c>
-      <c r="N40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O40" t="n">
+      <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD40" t="n">
         <v>2.25</v>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="AE40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.5</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH40" t="n">
-        <v>4.73</v>
+        <v>3.9</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.11</v>
+        <v>1.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC41" t="n">
         <v>1.79</v>
       </c>
-      <c r="P41" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V41" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AD41" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.58</v>
+        <v>1.84</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.32</v>
+        <v>2.15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.66</v>
+        <v>3.08</v>
       </c>
       <c r="N45" t="n">
-        <v>1.83</v>
+        <v>3.03</v>
       </c>
       <c r="O45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S45" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="U45" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V45" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="W45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AI45" t="n">
         <v>1.13</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6573,27 +6573,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="M47" t="n">
-        <v>3.85</v>
+        <v>3.99</v>
       </c>
       <c r="N47" t="n">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="O47" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="P47" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S47" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="T47" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="U47" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V47" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="W47" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF47" t="n">
         <v>1.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="AL47" s="3" t="n">
-        <v>45884.54166666666</v>
+        <v>45884.5625</v>
       </c>
     </row>
     <row r="48">
@@ -6705,27 +6705,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45884.5625</v>
+        <v>45884.57291666666</v>
       </c>
     </row>
     <row r="49">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>45884.57291666666</v>
+        <v>45884.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.32</v>
+        <v>6.3</v>
       </c>
       <c r="M50" t="n">
-        <v>3.03</v>
+        <v>5.2</v>
       </c>
       <c r="N50" t="n">
-        <v>2.79</v>
+        <v>1.3</v>
       </c>
       <c r="O50" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P50" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE50" t="n">
         <v>1.93</v>
       </c>
-      <c r="P50" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V50" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF50" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AH50" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD51" t="n">
         <v>3.55</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3</v>
-      </c>
       <c r="AE51" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>6.3</v>
+        <v>3.55</v>
       </c>
       <c r="M52" t="n">
-        <v>5.2</v>
+        <v>3.36</v>
       </c>
       <c r="N52" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>3.32</v>
+        <v>2.3</v>
       </c>
       <c r="P52" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="R52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.14</v>
-      </c>
-      <c r="S52" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.41</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="M53" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="P53" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="R53" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T53" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U53" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V53" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="W53" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AB53" t="n">
         <v>2.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH53" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7629,12 +7629,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="AL55" s="3" t="n">
-        <v>45884.58333333334</v>
+        <v>45884.60416666666</v>
       </c>
     </row>
     <row r="56">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,76 +8198,76 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N62" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P62" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R62" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S62" t="n">
         <v>2.6</v>
       </c>
       <c r="T62" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="U62" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V62" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="W62" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X62" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD62" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH62" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,76 +8726,76 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="M63" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="O63" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R63" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="S63" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="T63" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="U63" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V63" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y63" t="n">
         <v>9</v>
       </c>
-      <c r="W63" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>5.8</v>
-      </c>
       <c r="Z63" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AD63" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="n">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="AI63" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,76 +8858,76 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,76 +9386,76 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.82</v>
+        <v>1.25</v>
       </c>
       <c r="M68" t="n">
-        <v>3.01</v>
+        <v>5.25</v>
       </c>
       <c r="N68" t="n">
-        <v>2.31</v>
+        <v>8.5</v>
       </c>
       <c r="O68" t="n">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="P68" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="R68" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S68" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="T68" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="U68" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="V68" t="n">
-        <v>8.4</v>
+        <v>4.65</v>
       </c>
       <c r="W68" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X68" t="n">
         <v>1.01</v>
       </c>
-      <c r="X68" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AA68" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AB68" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.65</v>
+        <v>2.57</v>
       </c>
       <c r="AD68" t="n">
-        <v>4</v>
+        <v>2.11</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="n">
-        <v>8</v>
+        <v>3.55</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="M69" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="N69" t="n">
-        <v>2.48</v>
+        <v>6</v>
       </c>
       <c r="O69" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="P69" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>3.42</v>
       </c>
       <c r="R69" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S69" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="T69" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="U69" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V69" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="W69" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X69" t="n">
         <v>1.01</v>
       </c>
       <c r="Y69" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="Z69" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI69" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.16</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,76 +9650,76 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M70" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S70" t="n">
         <v>3.25</v>
       </c>
-      <c r="N70" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P70" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S70" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T70" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U70" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V70" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="W70" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X70" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y70" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AA70" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AD70" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AH70" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9778,80 +9778,80 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,76 +9914,76 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.25</v>
+        <v>2.82</v>
       </c>
       <c r="M72" t="n">
-        <v>5.25</v>
+        <v>3.01</v>
       </c>
       <c r="N72" t="n">
-        <v>8.5</v>
+        <v>2.31</v>
       </c>
       <c r="O72" t="n">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="P72" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="R72" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S72" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="T72" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="U72" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="V72" t="n">
-        <v>4.65</v>
+        <v>8.4</v>
       </c>
       <c r="W72" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y72" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AA72" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.57</v>
+        <v>1.65</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.11</v>
+        <v>4</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH72" t="n">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,76 +10046,76 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,76 +10178,76 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M74" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P74" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q74" t="n">
         <v>2.4</v>
       </c>
-      <c r="O74" t="n">
-        <v>2</v>
-      </c>
-      <c r="P74" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R74" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S74" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T74" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U74" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W74" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X74" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AA74" t="n">
-        <v>5.05</v>
+        <v>3.3</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.39</v>
+        <v>1.77</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="AH74" t="n">
-        <v>3.76</v>
+        <v>7</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10306,80 +10306,80 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.66</v>
+        <v>1.9</v>
       </c>
       <c r="M75" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="O75" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="P75" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="R75" t="n">
         <v>1.29</v>
       </c>
       <c r="S75" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T75" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="U75" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V75" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="W75" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X75" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y75" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA75" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH75" t="n">
-        <v>5</v>
+        <v>4.47</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,76 +10442,76 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="M76" t="n">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="N76" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="P76" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="R76" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S76" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="T76" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U76" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W76" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X76" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y76" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AA76" t="n">
-        <v>3.3</v>
+        <v>5.05</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AH76" t="n">
-        <v>6.5</v>
+        <v>3.76</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.8</v>
+        <v>2.66</v>
       </c>
       <c r="M77" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>3.7</v>
+        <v>2.48</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,76 +10838,76 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="M79" t="n">
-        <v>2.93</v>
+        <v>3.74</v>
       </c>
       <c r="N79" t="n">
-        <v>2.51</v>
+        <v>2.96</v>
       </c>
       <c r="O79" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="P79" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R79" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="S79" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="T79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U79" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V79" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="W79" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X79" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y79" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="Z79" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AB79" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA79" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC79" t="n">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="AD79" t="n">
-        <v>4.2</v>
+        <v>2.11</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="AH79" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,76 +10970,76 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="M80" t="n">
-        <v>3.74</v>
+        <v>2.93</v>
       </c>
       <c r="N80" t="n">
-        <v>2.96</v>
+        <v>2.51</v>
       </c>
       <c r="O80" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R80" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V80" t="n">
+        <v>8</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE80" t="n">
         <v>1.22</v>
       </c>
-      <c r="S80" t="n">
-        <v>4</v>
-      </c>
-      <c r="T80" t="n">
-        <v>2</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V80" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X80" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AF80" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AH80" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,52 +11102,52 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="N81" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="O81" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="P81" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="R81" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U81" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V81" t="n">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="W81" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X81" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y81" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AA81" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AB81" t="n">
         <v>1.85</v>
@@ -11156,22 +11156,22 @@
         <v>1.85</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG81" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AH81" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="M83" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O83" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="P83" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="R83" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S83" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="T83" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="U83" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="V83" t="n">
         <v>4.8</v>
       </c>
       <c r="W83" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X83" t="n">
         <v>1.01</v>
       </c>
       <c r="Y83" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z83" t="n">
         <v>1.11</v>
       </c>
       <c r="AA83" t="n">
-        <v>5.5</v>
+        <v>4.99</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC83" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD83" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD83" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AE83" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AG83" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH83" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="M87" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N87" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O87" t="n">
         <v>1.85</v>
@@ -11909,61 +11909,61 @@
         <v>8.5</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R87" t="n">
         <v>1.33</v>
       </c>
       <c r="S87" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="T87" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="U87" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V87" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W87" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X87" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y87" t="n">
         <v>8.5</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AA87" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="n">
-        <v>5.32</v>
+        <v>5.8</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,76 +12422,76 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AI91" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,76 +12554,76 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12682,80 +12682,80 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.68</v>
+        <v>3.64</v>
       </c>
       <c r="M93" t="n">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="N93" t="n">
-        <v>4.7</v>
+        <v>1.77</v>
       </c>
       <c r="O93" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R93" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S93" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U93" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V93" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W93" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X93" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AA93" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB93" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD93" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AF93" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AH93" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12814,80 +12814,80 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>7.6</v>
+        <v>3.41</v>
       </c>
       <c r="M94" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="N94" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="O94" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="R94" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S94" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T94" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U94" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V94" t="n">
         <v>6</v>
       </c>
       <c r="W94" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X94" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AA94" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH94" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AI94" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12946,80 +12946,80 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI95" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,76 +13082,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13210,80 +13210,80 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI97" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,76 +14534,76 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,76 +14798,76 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI109" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15335,13 +15335,13 @@
         <v>3.68</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R113" t="n">
         <v>1.73</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15476,58 +15476,58 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI114" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15608,58 +15608,58 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.23</v>
+        <v>3.69</v>
       </c>
       <c r="M4" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
         <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE4" t="n">
         <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
         <v>7.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.69</v>
+        <v>2.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N5" t="n">
-        <v>1.84</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T5" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE5" t="n">
         <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="n">
         <v>7.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.95</v>
       </c>
-      <c r="P6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="P7" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.42</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.08</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.07</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,40 +3182,40 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3242,10 +3242,10 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,70 +3314,70 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.33</v>
+        <v>3.38</v>
       </c>
       <c r="M24" t="n">
-        <v>3.26</v>
+        <v>3.09</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,70 +3710,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="M25" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.12</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>9.85</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.38</v>
+        <v>2.33</v>
       </c>
       <c r="M26" t="n">
-        <v>3.09</v>
+        <v>3.26</v>
       </c>
       <c r="N26" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N35" t="n">
-        <v>4.33</v>
+        <v>8.9</v>
       </c>
       <c r="O35" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="P35" t="n">
-        <v>9.5</v>
+        <v>13.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V35" t="n">
-        <v>6.3</v>
+        <v>5.55</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>7.8</v>
+        <v>13.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AH35" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.27</v>
       </c>
-      <c r="M36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P36" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="AA36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.3</v>
       </c>
-      <c r="S36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V36" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AF36" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5312,58 +5312,58 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.5</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH40" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="M41" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="N41" t="n">
-        <v>2.87</v>
+        <v>3.78</v>
       </c>
       <c r="O41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.11</v>
+        <v>3.02</v>
       </c>
       <c r="M42" t="n">
-        <v>3.78</v>
+        <v>2.98</v>
       </c>
       <c r="N42" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="O42" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>18.75</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="T42" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>4.65</v>
+        <v>5.95</v>
       </c>
       <c r="W42" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X42" t="n">
         <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AA42" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O43" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T43" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="V43" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.3</v>
+        <v>4.73</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>3.32</v>
       </c>
       <c r="M44" t="n">
-        <v>3.92</v>
+        <v>3.66</v>
       </c>
       <c r="N44" t="n">
-        <v>3.78</v>
+        <v>1.83</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O46" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S46" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U46" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="V46" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="W46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AI46" t="n">
         <v>1.1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.14</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.54</v>
+        <v>2.11</v>
       </c>
       <c r="M47" t="n">
-        <v>3.32</v>
+        <v>3.78</v>
       </c>
       <c r="N47" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="O47" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="P47" t="n">
-        <v>10</v>
+        <v>18.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="R47" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S47" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="T47" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V47" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="W47" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X47" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.32</v>
+        <v>6.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.03</v>
+        <v>5.2</v>
       </c>
       <c r="N51" t="n">
-        <v>2.79</v>
+        <v>1.3</v>
       </c>
       <c r="O51" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P51" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1.93</v>
       </c>
-      <c r="P51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AH51" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>6.3</v>
+        <v>2.32</v>
       </c>
       <c r="M53" t="n">
-        <v>5.2</v>
+        <v>3.03</v>
       </c>
       <c r="N53" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AE53" t="n">
         <v>1.3</v>
       </c>
-      <c r="O53" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P53" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S53" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF53" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>11</v>
+        <v>3.1</v>
       </c>
       <c r="O54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P54" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V54" t="n">
+        <v>9</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AE54" t="n">
         <v>1.25</v>
       </c>
-      <c r="P54" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V54" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF54" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AH54" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>1.19</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N55" t="n">
+        <v>11</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S55" t="n">
         <v>3.1</v>
       </c>
-      <c r="O55" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P55" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q55" t="n">
+      <c r="T55" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF55" t="n">
         <v>2.2</v>
       </c>
-      <c r="R55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V55" t="n">
-        <v>9</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG55" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AH55" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,76 +8198,76 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P59" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S59" t="n">
         <v>2.6</v>
       </c>
-      <c r="M59" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N59" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O59" t="n">
-        <v>2</v>
-      </c>
-      <c r="P59" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2.52</v>
-      </c>
       <c r="T59" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U59" t="n">
         <v>1.3</v>
       </c>
       <c r="V59" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="W59" t="n">
         <v>1.06</v>
       </c>
       <c r="X59" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH59" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N62" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P62" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R62" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S62" t="n">
         <v>2.6</v>
       </c>
       <c r="T62" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="U62" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V62" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="W62" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X62" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD62" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH62" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,76 +8726,76 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,76 +8858,76 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,76 +8990,76 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="M69" t="n">
         <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9646,80 +9646,80 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="M70" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="O70" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="P70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R70" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V70" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z70" t="n">
         <v>1.22</v>
       </c>
-      <c r="S70" t="n">
-        <v>4</v>
-      </c>
-      <c r="T70" t="n">
-        <v>2</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V70" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W70" t="n">
+      <c r="AA70" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AI70" t="n">
         <v>1.18</v>
-      </c>
-      <c r="X70" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.27</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,76 +9782,76 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,76 +9914,76 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M72" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N72" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="O72" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="P72" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S72" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="T72" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="U72" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V72" t="n">
-        <v>6.45</v>
+        <v>5.3</v>
       </c>
       <c r="W72" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X72" t="n">
         <v>1.01</v>
       </c>
       <c r="Y72" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AD72" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AH72" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,76 +10046,76 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.4</v>
+        <v>2.82</v>
       </c>
       <c r="M73" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>2.31</v>
       </c>
       <c r="O73" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="P73" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.42</v>
+        <v>2.05</v>
       </c>
       <c r="R73" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="S73" t="n">
-        <v>3.56</v>
+        <v>2.6</v>
       </c>
       <c r="T73" t="n">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V73" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="W73" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="X73" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y73" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AA73" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH73" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,76 +10178,76 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10306,80 +10306,80 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
         <v>3.7</v>
       </c>
       <c r="O75" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,76 +10442,76 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="M76" t="n">
-        <v>2.93</v>
+        <v>3.74</v>
       </c>
       <c r="N76" t="n">
-        <v>2.51</v>
+        <v>2.96</v>
       </c>
       <c r="O76" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="P76" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R76" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="S76" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V76" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="W76" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X76" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y76" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="Z76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AB76" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA76" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC76" t="n">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="AD76" t="n">
-        <v>4.2</v>
+        <v>2.11</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="AH76" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N78" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O78" t="n">
+        <v>2</v>
+      </c>
+      <c r="P78" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q78" t="n">
         <v>1.95</v>
       </c>
-      <c r="P78" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1.91</v>
-      </c>
       <c r="R78" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S78" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T78" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="U78" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V78" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="W78" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X78" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y78" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AA78" t="n">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH78" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,76 +10838,76 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="M79" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N79" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="P79" t="n">
         <v>11</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="R79" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S79" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T79" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U79" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V79" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W79" t="n">
         <v>1.17</v>
       </c>
       <c r="X79" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79" t="n">
         <v>10</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AA79" t="n">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="AB79" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF79" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC79" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG79" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH79" t="n">
-        <v>3.76</v>
+        <v>3.96</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,76 +10970,76 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="M80" t="n">
-        <v>4.1</v>
+        <v>2.93</v>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>2.51</v>
       </c>
       <c r="O80" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R80" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="S80" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="T80" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="U80" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="V80" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="W80" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X80" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y80" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AA80" t="n">
-        <v>4.99</v>
+        <v>2.9</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.46</v>
+        <v>1.61</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH80" t="n">
-        <v>3.96</v>
+        <v>8</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,76 +11102,76 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="M81" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>8.5</v>
+        <v>2.99</v>
       </c>
       <c r="O81" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P81" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V81" t="n">
+        <v>8</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE81" t="n">
         <v>1.28</v>
       </c>
-      <c r="P81" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R81" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S81" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T81" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V81" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W81" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X81" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z81" t="n">
+      <c r="AF81" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI81" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>1.24</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,76 +11234,76 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="M82" t="n">
-        <v>3.51</v>
+        <v>5.25</v>
       </c>
       <c r="N82" t="n">
-        <v>4.3</v>
+        <v>8.5</v>
       </c>
       <c r="O82" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="P82" t="n">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="R82" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V82" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB82" t="n">
         <v>1.4</v>
       </c>
-      <c r="S82" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T82" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U82" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V82" t="n">
-        <v>7</v>
-      </c>
-      <c r="W82" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X82" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC82" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.4</v>
+        <v>2.11</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH82" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,22 +11498,22 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>3.51</v>
       </c>
       <c r="N84" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="O84" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="P84" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R84" t="n">
         <v>1.4</v>
@@ -11528,16 +11528,16 @@
         <v>1.4</v>
       </c>
       <c r="V84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W84" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X84" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y84" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z84" t="n">
         <v>1.33</v>
@@ -11546,28 +11546,28 @@
         <v>3.3</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC84" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF84" t="n">
         <v>1.77</v>
       </c>
-      <c r="AD84" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG84" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH84" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.56</v>
+        <v>2.29</v>
       </c>
       <c r="M85" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P85" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S85" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V85" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD85" t="n">
         <v>4.2</v>
       </c>
-      <c r="N85" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P85" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S85" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V85" t="n">
-        <v>5</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X85" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE85" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AH85" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,76 +11762,76 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="M86" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="N86" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O86" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="P86" t="n">
-        <v>7.3</v>
+        <v>16.25</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="R86" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="S86" t="n">
-        <v>2.61</v>
+        <v>3.34</v>
       </c>
       <c r="T86" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="U86" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="V86" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="W86" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X86" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.3</v>
+        <v>15</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.87</v>
+        <v>4.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="AD86" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AH86" t="n">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,76 +12158,76 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AI90" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>10.05</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12682,80 +12682,80 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>7.6</v>
+        <v>3.41</v>
       </c>
       <c r="M93" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="N93" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="O93" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="R93" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S93" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T93" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U93" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V93" t="n">
         <v>6</v>
       </c>
       <c r="W93" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X93" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AA93" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC93" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12814,80 +12814,80 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,76 +13082,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13210,80 +13210,80 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.68</v>
+        <v>3.64</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="N97" t="n">
-        <v>4.7</v>
+        <v>1.77</v>
       </c>
       <c r="O97" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R97" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S97" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="T97" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U97" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V97" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W97" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X97" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AA97" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB97" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD97" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AH97" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13342,80 +13342,80 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.64</v>
+        <v>7.6</v>
       </c>
       <c r="M98" t="n">
-        <v>3.57</v>
+        <v>4.33</v>
       </c>
       <c r="N98" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="O98" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="P98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="R98" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S98" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T98" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U98" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V98" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W98" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X98" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z98" t="n">
         <v>1.2</v>
       </c>
       <c r="AA98" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG98" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH98" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI98" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,76 +13478,76 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,76 +13610,76 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AI100" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,76 +13742,76 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="M101" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N101" t="n">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="O101" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="P101" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R101" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="T101" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="U101" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="V101" t="n">
-        <v>4.33</v>
+        <v>5.4</v>
       </c>
       <c r="W101" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X101" t="n">
         <v>1.01</v>
       </c>
       <c r="Y101" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AA101" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AC101" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD101" t="n">
         <v>2.75</v>
       </c>
-      <c r="AD101" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE101" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG101" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH101" t="n">
-        <v>3.22</v>
+        <v>5.2</v>
       </c>
       <c r="AI101" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,76 +14666,76 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="M108" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N108" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R108" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S108" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="T108" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U108" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V108" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W108" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X108" t="n">
         <v>1.05</v>
       </c>
       <c r="Y108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AD108" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG108" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH108" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,76 +15062,76 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH111" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI111" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15212,58 +15212,58 @@
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI112" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15608,58 +15608,58 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V115" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI115" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15740,58 +15740,58 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W116" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG116" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH116" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI116" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.09</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O2" t="n">
         <v>2.6</v>
@@ -725,7 +725,7 @@
         <v>1.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
         <v>2.85</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,73 +938,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.04</v>
+        <v>3.38</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>2.57</v>
       </c>
       <c r="O4" t="n">
         <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Z4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI4" t="n">
         <v>1.08</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.69</v>
+        <v>2.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="n">
         <v>7.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>3.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>2.57</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.57</v>
@@ -1646,10 +1646,10 @@
         <v>3.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
         <v>3</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,40 +2918,40 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.38</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.09</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.26</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.65</v>
@@ -3335,10 +3335,10 @@
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
         <v>1.54</v>
@@ -3353,34 +3353,34 @@
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
         <v>1.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
         <v>2.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AI22" t="n">
         <v>1.18</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,40 +3446,40 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.55</v>
+        <v>3.38</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3506,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="N30" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="O30" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>18.75</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="U30" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="V30" t="n">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AA30" t="n">
-        <v>5.2</v>
+        <v>4.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4652,58 +4652,58 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.27</v>
+        <v>2.19</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>8.9</v>
+        <v>2.62</v>
       </c>
       <c r="O33" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
       <c r="P33" t="n">
-        <v>13.75</v>
+        <v>18.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>2.03</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
         <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>13.9</v>
+        <v>14.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.94</v>
+        <v>5.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,67 +4898,67 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.3</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="U34" t="n">
         <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.5</v>
+        <v>13.4</v>
       </c>
       <c r="Z34" t="n">
         <v>1.17</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.3</v>
+        <v>4.54</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG34" t="n">
         <v>2.25</v>
@@ -4967,7 +4967,7 @@
         <v>4.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.32</v>
+        <v>1.66</v>
       </c>
       <c r="M35" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="O35" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="U35" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="W35" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.47</v>
+        <v>5.8</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>3.78</v>
+        <v>2.01</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N40" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="O40" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R40" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
         <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="U40" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V40" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>5.5</v>
+        <v>4.47</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,25 +5822,25 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="M41" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
         <v>3.1</v>
@@ -5852,43 +5852,43 @@
         <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W41" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC41" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AI41" t="n">
         <v>1.14</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>4.33</v>
+        <v>2.32</v>
       </c>
       <c r="O42" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="P42" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="R42" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="U42" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.54</v>
+        <v>1.18</v>
       </c>
       <c r="M43" t="n">
-        <v>3.32</v>
+        <v>5.5</v>
       </c>
       <c r="N43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P43" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF43" t="n">
         <v>2.35</v>
       </c>
-      <c r="O43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="AG43" t="n">
         <v>1.5</v>
       </c>
-      <c r="V43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="M44" t="n">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
         <v>1.57</v>
@@ -6236,10 +6236,10 @@
         <v>2.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
         <v>2.15</v>
@@ -6260,16 +6260,16 @@
         <v>14.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AB44" t="n">
         <v>1.46</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AD44" t="n">
         <v>2.2</v>
@@ -6284,7 +6284,7 @@
         <v>2.35</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AI44" t="n">
         <v>1.22</v>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M46" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="N46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O46" t="n">
         <v>1.25</v>
@@ -6530,16 +6530,16 @@
         <v>4.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD46" t="n">
         <v>2.8</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF46" t="n">
         <v>2.2</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="M47" t="n">
-        <v>5.2</v>
+        <v>3.42</v>
       </c>
       <c r="N47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3</v>
+      </c>
+      <c r="P47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.3</v>
       </c>
-      <c r="O47" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P47" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V47" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="W47" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="AA47" t="n">
-        <v>7.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.2</v>
+        <v>1.63</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.77</v>
+        <v>3.9</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD49" t="n">
         <v>3.55</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P49" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V49" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3</v>
-      </c>
       <c r="AE49" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="M50" t="n">
-        <v>3.41</v>
+        <v>5.2</v>
       </c>
       <c r="N50" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="P50" t="n">
-        <v>7.5</v>
+        <v>33</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="R50" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="S50" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="T50" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="V50" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X50" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>7.5</v>
+        <v>29</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.74</v>
+        <v>7.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.9</v>
+        <v>1.77</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AH50" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="M51" t="n">
-        <v>3.03</v>
+        <v>3.36</v>
       </c>
       <c r="N51" t="n">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="O51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC51" t="n">
         <v>1.93</v>
       </c>
-      <c r="P51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R51" t="n">
+      <c r="AD51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1.4</v>
       </c>
-      <c r="S51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH51" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="M55" t="n">
         <v>2.85</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="O55" t="n">
         <v>1.93</v>
@@ -7715,13 +7715,13 @@
         <v>1.47</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AB55" t="n">
         <v>2.58</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AD55" t="n">
         <v>4.91</v>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="M58" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="O58" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="P58" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R58" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="S58" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="T58" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U58" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W58" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X58" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y58" t="n">
-        <v>6.45</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF58" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,76 +8462,76 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8986,80 +8986,80 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="M65" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD65" t="n">
         <v>2.51</v>
       </c>
-      <c r="O65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P65" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V65" t="n">
-        <v>8</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X65" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AE65" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="n">
-        <v>8</v>
+        <v>4.47</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,76 +9122,76 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.66</v>
+        <v>1.4</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N66" t="n">
-        <v>2.48</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.91</v>
+        <v>3.42</v>
       </c>
       <c r="R66" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S66" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="T66" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="U66" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V66" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="W66" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X66" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AA66" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,76 +9254,76 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>2.87</v>
       </c>
       <c r="O67" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="P67" t="n">
         <v>11</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R67" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S67" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T67" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U67" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V67" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="W67" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X67" t="n">
         <v>1.01</v>
       </c>
       <c r="Y67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AA67" t="n">
-        <v>4.99</v>
+        <v>5.25</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD67" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG67" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH67" t="n">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9382,80 +9382,80 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="M68" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="O68" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="R68" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S68" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T68" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U68" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V68" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="W68" t="n">
         <v>1.12</v>
       </c>
       <c r="X68" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y68" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z68" t="n">
         <v>1.22</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AD68" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="n">
-        <v>4.47</v>
+        <v>5.05</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M69" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>8.5</v>
+        <v>3.7</v>
       </c>
       <c r="O69" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.57</v>
+        <v>1.68</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,76 +9650,76 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.9</v>
+        <v>1.64</v>
       </c>
       <c r="M70" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P70" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S70" t="n">
         <v>3.4</v>
       </c>
-      <c r="N70" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O70" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P70" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S70" t="n">
-        <v>2.98</v>
-      </c>
       <c r="T70" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="U70" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="V70" t="n">
-        <v>6.45</v>
+        <v>5.05</v>
       </c>
       <c r="W70" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X70" t="n">
         <v>1.01</v>
       </c>
       <c r="Y70" t="n">
-        <v>9</v>
+        <v>14.2</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AA70" t="n">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AD70" t="n">
-        <v>3.08</v>
+        <v>2.31</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AH70" t="n">
-        <v>5.9</v>
+        <v>3.96</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,76 +9782,76 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>3.01</v>
       </c>
       <c r="N71" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="O71" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="P71" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R71" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S71" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T71" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="U71" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V71" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="W71" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="X71" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AA71" t="n">
-        <v>5.05</v>
+        <v>3</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AD71" t="n">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG71" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="n">
-        <v>3.76</v>
+        <v>8</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,76 +9914,76 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M72" t="n">
+        <v>5</v>
+      </c>
+      <c r="N72" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P72" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U72" t="n">
         <v>1.67</v>
       </c>
-      <c r="M72" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N72" t="n">
+      <c r="V72" t="n">
         <v>4.3</v>
       </c>
-      <c r="O72" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P72" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V72" t="n">
-        <v>7</v>
-      </c>
       <c r="W72" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X72" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y72" t="n">
-        <v>8.5</v>
+        <v>14.2</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AD72" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH72" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,76 +10046,76 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="M73" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N73" t="n">
-        <v>4.2</v>
+        <v>2.99</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,76 +10178,76 @@
         </is>
       </c>
       <c r="L74" t="n">
+        <v>11</v>
+      </c>
+      <c r="M74" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V74" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD74" t="n">
         <v>2.1</v>
       </c>
-      <c r="M74" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N74" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P74" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T74" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U74" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V74" t="n">
-        <v>8</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X74" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AE74" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH74" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,76 +10310,76 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.82</v>
+        <v>1.73</v>
       </c>
       <c r="M75" t="n">
-        <v>3.01</v>
+        <v>3.36</v>
       </c>
       <c r="N75" t="n">
-        <v>2.31</v>
+        <v>4.5</v>
       </c>
       <c r="O75" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="P75" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R75" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S75" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="T75" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="U75" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V75" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y75" t="n">
         <v>8.4</v>
       </c>
-      <c r="W75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X75" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>8</v>
-      </c>
       <c r="Z75" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AA75" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AD75" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH75" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,76 +10442,76 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AI76" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M77" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N77" t="n">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="O77" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="P77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q77" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R77" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T77" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="U77" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="V77" t="n">
-        <v>5.6</v>
+        <v>4.75</v>
       </c>
       <c r="W77" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X77" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y77" t="n">
-        <v>11.5</v>
+        <v>13.8</v>
       </c>
       <c r="Z77" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AI77" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>1.13</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="M78" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="O78" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="P78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="R78" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>2.69</v>
       </c>
       <c r="U78" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="V78" t="n">
-        <v>4.5</v>
+        <v>6.45</v>
       </c>
       <c r="W78" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X78" t="n">
         <v>1.01</v>
       </c>
       <c r="Y78" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AA78" t="n">
-        <v>5.91</v>
+        <v>3.34</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.11</v>
+        <v>3.08</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.62</v>
+        <v>2.02</v>
       </c>
       <c r="AH78" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,76 +10838,76 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="M79" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V79" t="n">
+        <v>7</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD79" t="n">
         <v>3.4</v>
       </c>
-      <c r="N79" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,76 +10970,76 @@
         </is>
       </c>
       <c r="L80" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P80" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V80" t="n">
+        <v>8</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z80" t="n">
         <v>1.4</v>
       </c>
-      <c r="M80" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N80" t="n">
-        <v>6</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P80" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S80" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T80" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V80" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X80" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA80" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,76 +11102,76 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="M81" t="n">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="N81" t="n">
-        <v>4.8</v>
+        <v>2.56</v>
       </c>
       <c r="O81" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,76 +11234,76 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="M82" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB82" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG82" t="n">
         <v>1.79</v>
       </c>
-      <c r="AC82" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>0</v>
-      </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="M83" t="n">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O83" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="P83" t="n">
-        <v>7.3</v>
+        <v>16.25</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="R83" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V83" t="n">
+        <v>5</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X83" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE83" t="n">
         <v>1.44</v>
       </c>
-      <c r="S83" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T83" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U83" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V83" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W83" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X83" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF83" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AG83" t="n">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="AH83" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="M84" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="N84" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O84" t="n">
         <v>1.85</v>
@@ -11516,16 +11516,16 @@
         <v>2.25</v>
       </c>
       <c r="R84" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S84" t="n">
-        <v>2.81</v>
+        <v>3.03</v>
       </c>
       <c r="T84" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U84" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V84" t="n">
         <v>5.8</v>
@@ -11534,25 +11534,25 @@
         <v>1.05</v>
       </c>
       <c r="X84" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y84" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AA84" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD84" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AE84" t="n">
         <v>1.33</v>
@@ -11564,7 +11564,7 @@
         <v>2.1</v>
       </c>
       <c r="AH84" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="AI84" t="n">
         <v>1.11</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="M86" t="n">
-        <v>3.25</v>
+        <v>6.26</v>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>10.05</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,76 +11894,76 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI87" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="M88" t="n">
-        <v>6.26</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>10.05</v>
+        <v>4</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,76 +12158,76 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.42</v>
+        <v>3.64</v>
       </c>
       <c r="M89" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="N89" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="M90" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N90" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI90" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12418,80 +12418,80 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.41</v>
+        <v>1.68</v>
       </c>
       <c r="M91" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="N91" t="n">
-        <v>1.98</v>
+        <v>4.7</v>
       </c>
       <c r="O91" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="P91" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R91" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S91" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T91" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W91" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X91" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AA91" t="n">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.57</v>
+        <v>3.8</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AH91" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12550,80 +12550,80 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.68</v>
+        <v>3.41</v>
       </c>
       <c r="M92" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="N92" t="n">
-        <v>4.7</v>
+        <v>1.98</v>
       </c>
       <c r="O92" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R92" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S92" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T92" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U92" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W92" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X92" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AA92" t="n">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD92" t="n">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AF92" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG92" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="AI92" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,76 +12818,76 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.64</v>
+        <v>2.46</v>
       </c>
       <c r="M94" t="n">
-        <v>3.57</v>
+        <v>3.21</v>
       </c>
       <c r="N94" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="O94" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S94" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="T94" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U94" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V94" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W94" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X94" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AI94" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X94" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>1.18</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="M102" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N102" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
         <v>2.2</v>
@@ -13901,28 +13901,28 @@
         <v>3.5</v>
       </c>
       <c r="U102" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V102" t="n">
         <v>7.8</v>
       </c>
       <c r="W102" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X102" t="n">
         <v>1.11</v>
       </c>
       <c r="Y102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC102" t="n">
         <v>1.5</v>
@@ -13931,19 +13931,19 @@
         <v>4.65</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG102" t="n">
         <v>1.67</v>
       </c>
       <c r="AH102" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="AI102" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14420,58 +14420,58 @@
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI106" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14552,58 +14552,58 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="M109" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="N109" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="S109" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="T109" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U109" t="n">
         <v>1.18</v>
@@ -14837,19 +14837,19 @@
         <v>1.09</v>
       </c>
       <c r="Y109" t="n">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB109" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC109" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD109" t="n">
         <v>5.7</v>
@@ -14861,7 +14861,7 @@
         <v>2.45</v>
       </c>
       <c r="AG109" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AH109" t="n">
         <v>12.5</v>
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M110" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="N110" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="O110" t="n">
         <v>1.8</v>
@@ -14957,7 +14957,7 @@
         <v>4.5</v>
       </c>
       <c r="U110" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="V110" t="n">
         <v>19</v>
@@ -14975,10 +14975,10 @@
         <v>1.78</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB110" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AC110" t="n">
         <v>1.28</v>
@@ -14987,7 +14987,7 @@
         <v>6.8</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF110" t="n">
         <v>2.65</v>
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="M112" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="N112" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,7 +15242,7 @@
         <v>3.42</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC112" t="n">
         <v>1.85</v>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,73 +938,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="M4" t="n">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="N4" t="n">
-        <v>2.57</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
         <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.38</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH4" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI4" t="n">
         <v>1.08</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.23</v>
+        <v>3.69</v>
       </c>
       <c r="M6" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="U6" t="n">
         <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="n">
         <v>7.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.65</v>
       </c>
-      <c r="P7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.44</v>
       </c>
-      <c r="V9" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.55</v>
+        <v>3.95</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2782,74 +2782,74 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,40 +2918,40 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,70 +3446,70 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>3.09</v>
+        <v>2.81</v>
       </c>
       <c r="N23" t="n">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.19</v>
+        <v>1.18</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.62</v>
+        <v>11.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="P33" t="n">
-        <v>18.75</v>
+        <v>13.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.03</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC33" t="n">
         <v>2.2</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="Z33" t="n">
+      <c r="AD33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.22</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="O34" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="P34" t="n">
-        <v>9</v>
+        <v>18.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T34" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>13.4</v>
+        <v>14.7</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.54</v>
+        <v>5.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.59</v>
+        <v>2.26</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="P35" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="T35" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V35" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="O37" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R37" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="W37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.22</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>2.01</v>
+        <v>3.35</v>
       </c>
       <c r="O40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P40" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.3</v>
       </c>
-      <c r="P40" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.73</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="U40" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.47</v>
+        <v>4.7</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="O42" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="P42" t="n">
         <v>10</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="R42" t="n">
         <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="U42" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V42" t="n">
-        <v>5.6</v>
+        <v>5.85</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AA42" t="n">
         <v>4.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH42" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>11.5</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="P43" t="n">
-        <v>13.75</v>
+        <v>10</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="U43" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="W43" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AB43" t="n">
         <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.21</v>
+        <v>3.55</v>
       </c>
       <c r="M46" t="n">
-        <v>5.5</v>
+        <v>3.36</v>
       </c>
       <c r="N46" t="n">
-        <v>12</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="P46" t="n">
         <v>10</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="T46" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="U46" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V46" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
         <v>10</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG46" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH46" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M47" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="P47" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T47" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF47" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH47" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="O48" t="n">
-        <v>1.83</v>
+        <v>3.32</v>
       </c>
       <c r="P48" t="n">
-        <v>8.199999999999999</v>
+        <v>33</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="S48" t="n">
-        <v>2.63</v>
+        <v>4.4</v>
       </c>
       <c r="T48" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.05</v>
+        <v>7.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.64</v>
+        <v>1.77</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="AH48" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="M50" t="n">
-        <v>5.2</v>
+        <v>3.41</v>
       </c>
       <c r="N50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3</v>
+      </c>
+      <c r="P50" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U50" t="n">
         <v>1.3</v>
       </c>
-      <c r="O50" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P50" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S50" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V50" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="W50" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>7.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.77</v>
+        <v>3.9</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.55</v>
+        <v>1.19</v>
       </c>
       <c r="M51" t="n">
-        <v>3.36</v>
+        <v>5.2</v>
       </c>
       <c r="N51" t="n">
-        <v>1.85</v>
+        <v>11</v>
       </c>
       <c r="O51" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="P51" t="n">
         <v>10</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S51" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="T51" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="U51" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V51" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="W51" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X51" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
         <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AD51" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AH51" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P60" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S60" t="n">
         <v>2.6</v>
       </c>
-      <c r="M60" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N60" t="n">
+      <c r="T60" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V60" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA60" t="n">
         <v>2.83</v>
       </c>
-      <c r="O60" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P60" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V60" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X60" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AB60" t="n">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.7</v>
+        <v>3.92</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF60" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH60" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="O62" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="P62" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R62" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="S62" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T62" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U62" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V62" t="n">
-        <v>6.7</v>
+        <v>8.6</v>
       </c>
       <c r="W62" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X62" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y62" t="n">
-        <v>7.9</v>
+        <v>6.76</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AD62" t="n">
-        <v>3.92</v>
+        <v>4.7</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH62" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8986,80 +8986,80 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="M65" t="n">
-        <v>3.65</v>
+        <v>3.36</v>
       </c>
       <c r="N65" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S65" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="T65" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="U65" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V65" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH65" t="n">
         <v>5.5</v>
       </c>
-      <c r="W65" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X65" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>4.47</v>
-      </c>
       <c r="AI65" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,76 +9122,76 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.4</v>
+        <v>2.82</v>
       </c>
       <c r="M66" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>2.31</v>
       </c>
       <c r="O66" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="P66" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.42</v>
+        <v>2.05</v>
       </c>
       <c r="R66" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="S66" t="n">
-        <v>3.56</v>
+        <v>2.6</v>
       </c>
       <c r="T66" t="n">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V66" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="W66" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="X66" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y66" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AA66" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,76 +9254,76 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.92</v>
+        <v>11</v>
       </c>
       <c r="M67" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="N67" t="n">
-        <v>2.87</v>
+        <v>1.18</v>
       </c>
       <c r="O67" t="n">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="P67" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="R67" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S67" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T67" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="U67" t="n">
         <v>1.67</v>
       </c>
       <c r="V67" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="W67" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X67" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AA67" t="n">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AB67" t="n">
         <v>1.4</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD67" t="n">
         <v>2.1</v>
       </c>
       <c r="AE67" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG67" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>2.63</v>
       </c>
       <c r="AH67" t="n">
         <v>3.45</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M69" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N69" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,76 +9650,76 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="M70" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="O70" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="P70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
+        <v>2</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T70" t="n">
         <v>2.5</v>
       </c>
-      <c r="R70" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S70" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T70" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U70" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="V70" t="n">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="W70" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X70" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70" t="n">
-        <v>14.2</v>
+        <v>11.5</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AA70" t="n">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH70" t="n">
-        <v>3.96</v>
+        <v>5.15</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,73 +9782,73 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="M71" t="n">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O71" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="P71" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="R71" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="S71" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="T71" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U71" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V71" t="n">
-        <v>8.4</v>
+        <v>6.45</v>
       </c>
       <c r="W71" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X71" t="n">
         <v>1.01</v>
       </c>
-      <c r="X71" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AA71" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD71" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AH71" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="AI71" t="n">
         <v>1.07</v>
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,76 +9914,76 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="M72" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N72" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="O72" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="P72" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R72" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S72" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="T72" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U72" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="V72" t="n">
-        <v>4.3</v>
+        <v>5.05</v>
       </c>
       <c r="W72" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X72" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y72" t="n">
         <v>14.2</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AA72" t="n">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH72" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,76 +10046,76 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="M73" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N73" t="n">
-        <v>2.99</v>
+        <v>7.5</v>
       </c>
       <c r="O73" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P73" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U73" t="n">
         <v>1.67</v>
       </c>
-      <c r="P73" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T73" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V73" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="W73" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X73" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y73" t="n">
-        <v>9</v>
+        <v>14.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AA73" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AD73" t="n">
-        <v>3.5</v>
+        <v>2.19</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,76 +10178,76 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>11</v>
+        <v>2.1</v>
       </c>
       <c r="M74" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>1.18</v>
+        <v>2.99</v>
       </c>
       <c r="O74" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="R74" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S74" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="T74" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="U74" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V74" t="n">
-        <v>4.35</v>
+        <v>8</v>
       </c>
       <c r="W74" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X74" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y74" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AA74" t="n">
-        <v>5.15</v>
+        <v>3.3</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH74" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,76 +10310,76 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,76 +10442,76 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="M76" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V76" t="n">
+        <v>7</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD76" t="n">
         <v>3.4</v>
       </c>
-      <c r="N76" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P76" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>2</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S76" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V76" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X76" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AE76" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AH76" t="n">
-        <v>5.15</v>
+        <v>6.5</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="M78" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P78" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q78" t="n">
         <v>2.25</v>
       </c>
-      <c r="O78" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P78" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1.85</v>
-      </c>
       <c r="R78" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="S78" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="T78" t="n">
-        <v>2.69</v>
+        <v>2.13</v>
       </c>
       <c r="U78" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="V78" t="n">
-        <v>6.45</v>
+        <v>4.45</v>
       </c>
       <c r="W78" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="X78" t="n">
         <v>1.01</v>
       </c>
       <c r="Y78" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AA78" t="n">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD78" t="n">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE78" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AI78" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>1.07</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10834,80 +10834,80 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M79" t="n">
-        <v>3.51</v>
+        <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="O79" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V79" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB79" t="n">
         <v>1.65</v>
       </c>
-      <c r="P79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T79" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X79" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC79" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AD79" t="n">
-        <v>3.4</v>
+        <v>2.51</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,76 +11102,76 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="M81" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB81" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG81" t="n">
         <v>1.79</v>
       </c>
-      <c r="AC81" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>0</v>
-      </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,76 +11234,76 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="M82" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="N82" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O82" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="P82" t="n">
-        <v>7.3</v>
+        <v>16.25</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="R82" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S82" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T82" t="n">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="U82" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="V82" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="W82" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X82" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.84</v>
+        <v>2.5</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="AH82" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="M83" t="n">
-        <v>4.1</v>
+        <v>3.23</v>
       </c>
       <c r="N83" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="O83" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N84" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="O84" t="n">
         <v>1.85</v>
@@ -11513,61 +11513,61 @@
         <v>8.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R84" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V84" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X84" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AE84" t="n">
         <v>1.36</v>
       </c>
-      <c r="S84" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="T84" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U84" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V84" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF84" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG84" t="n">
         <v>2.1</v>
       </c>
       <c r="AH84" t="n">
-        <v>5.65</v>
+        <v>5.25</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>10.05</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,76 +11894,76 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.04</v>
+        <v>1.23</v>
       </c>
       <c r="M87" t="n">
-        <v>3.45</v>
+        <v>6.26</v>
       </c>
       <c r="N87" t="n">
-        <v>3.3</v>
+        <v>10.05</v>
       </c>
       <c r="O87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.91</v>
+        <v>2</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,76 +12158,76 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.64</v>
+        <v>2.46</v>
       </c>
       <c r="M89" t="n">
-        <v>3.57</v>
+        <v>3.21</v>
       </c>
       <c r="N89" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="O89" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S89" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="T89" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U89" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V89" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W89" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AI89" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X89" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI89" t="n">
-        <v>1.18</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.17</v>
+        <v>3.64</v>
       </c>
       <c r="M90" t="n">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="O90" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="R90" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S90" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T90" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U90" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="V90" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="W90" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X90" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y90" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="AD90" t="n">
-        <v>3.58</v>
+        <v>2.6</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AH90" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12550,80 +12550,80 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.41</v>
+        <v>7.6</v>
       </c>
       <c r="M92" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="N92" t="n">
-        <v>1.98</v>
+        <v>1.39</v>
       </c>
       <c r="O92" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="P92" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="R92" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S92" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T92" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U92" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V92" t="n">
         <v>6</v>
       </c>
       <c r="W92" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X92" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AA92" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC92" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD92" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG92" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH92" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AI92" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12682,80 +12682,80 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>7.6</v>
+        <v>2.17</v>
       </c>
       <c r="M93" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="N93" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="O93" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="R93" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S93" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="T93" t="n">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="U93" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V93" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="W93" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X93" t="n">
         <v>1.01</v>
       </c>
       <c r="Y93" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AA93" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC93" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AF93" t="n">
         <v>1.83</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH93" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,73 +12818,73 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.46</v>
+        <v>3.41</v>
       </c>
       <c r="M94" t="n">
-        <v>3.21</v>
+        <v>3.68</v>
       </c>
       <c r="N94" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R94" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S94" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T94" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U94" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V94" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W94" t="n">
         <v>1.13</v>
       </c>
       <c r="X94" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y94" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA94" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AG94" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AH94" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AI94" t="n">
         <v>1.12</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,76 +12950,76 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AI95" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,76 +13082,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,76 +13214,76 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="M97" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N97" t="n">
+        <v>8</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P97" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="n">
         <v>3.25</v>
       </c>
-      <c r="O97" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P97" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R97" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S97" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="T97" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="U97" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="V97" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="W97" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X97" t="n">
         <v>1.01</v>
       </c>
       <c r="Y97" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AA97" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="AD97" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG97" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH97" t="n">
-        <v>5.2</v>
+        <v>3.22</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M103" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="N103" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="O103" t="n">
         <v>1.83</v>
@@ -14054,10 +14054,10 @@
         <v>3.1</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AD103" t="n">
         <v>3.6</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14420,58 +14420,58 @@
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI106" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14552,58 +14552,58 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH107" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI107" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G108" t="n">

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.23</v>
+        <v>3.69</v>
       </c>
       <c r="M4" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
         <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE4" t="n">
         <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
         <v>7.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.42</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V5" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.07</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.69</v>
+        <v>2.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="n">
         <v>7.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.95</v>
       </c>
-      <c r="P7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="O20" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="P20" t="n">
-        <v>17.5</v>
+        <v>6.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>3.68</v>
       </c>
       <c r="U20" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>5.45</v>
+        <v>9.85</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>6.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.6</v>
+        <v>2.39</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH20" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,70 +3446,70 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4.33</v>
+        <v>11.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="P32" t="n">
-        <v>9.5</v>
+        <v>13.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.4</v>
       </c>
-      <c r="V32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="M33" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>11.5</v>
+        <v>2.32</v>
       </c>
       <c r="O33" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="P33" t="n">
-        <v>13.75</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AB33" t="n">
         <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,28 +4898,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="P34" t="n">
-        <v>18.75</v>
+        <v>14</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="T34" t="n">
         <v>2.2</v>
@@ -4928,16 +4928,16 @@
         <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>14.7</v>
+        <v>17</v>
       </c>
       <c r="Z34" t="n">
         <v>1.15</v>
@@ -4946,25 +4946,25 @@
         <v>5.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG34" t="n">
         <v>2.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" t="n">
         <v>1.22</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,28 +5030,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="O35" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="P35" t="n">
-        <v>14</v>
+        <v>18.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="R35" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
         <v>2.2</v>
@@ -5060,16 +5060,16 @@
         <v>1.62</v>
       </c>
       <c r="V35" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>17</v>
+        <v>14.7</v>
       </c>
       <c r="Z35" t="n">
         <v>1.15</v>
@@ -5078,25 +5078,25 @@
         <v>5.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG35" t="n">
         <v>2.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AI35" t="n">
         <v>1.22</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="M38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P38" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
         <v>3.3</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2</v>
-      </c>
-      <c r="P38" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.89</v>
-      </c>
       <c r="T38" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>13.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.9</v>
+        <v>4.54</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC38" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG38" t="n">
         <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="O40" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S40" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T40" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="U40" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V40" t="n">
-        <v>5</v>
+        <v>5.85</v>
       </c>
       <c r="W40" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>13.4</v>
+        <v>8</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="N42" t="n">
-        <v>2.96</v>
+        <v>2.01</v>
       </c>
       <c r="O42" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="P42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="R42" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="U42" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>5.85</v>
+        <v>5.1</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AH42" t="n">
-        <v>5.3</v>
+        <v>4.47</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P43" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.6</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.35</v>
-      </c>
       <c r="U43" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="W43" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="M46" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="O46" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="P46" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="T46" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="V46" t="n">
-        <v>6.1</v>
+        <v>9</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AD46" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH46" t="n">
-        <v>5.75</v>
+        <v>7.1</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="O47" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="P47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q47" t="n">
         <v>2.2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA47" t="n">
         <v>3.25</v>
       </c>
-      <c r="U47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V47" t="n">
-        <v>9</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AB47" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC47" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF47" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD47" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG47" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="M48" t="n">
-        <v>5.2</v>
+        <v>3.41</v>
       </c>
       <c r="N48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3</v>
+      </c>
+      <c r="P48" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U48" t="n">
         <v>1.3</v>
       </c>
-      <c r="O48" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P48" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S48" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V48" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>7.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.77</v>
+        <v>3.9</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.32</v>
+        <v>6.3</v>
       </c>
       <c r="M49" t="n">
-        <v>3.03</v>
+        <v>5.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.79</v>
+        <v>1.3</v>
       </c>
       <c r="O49" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P49" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE49" t="n">
         <v>1.93</v>
       </c>
-      <c r="P49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V49" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF49" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AH49" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>5.4</v>
+        <v>1.19</v>
       </c>
       <c r="M50" t="n">
-        <v>3.41</v>
+        <v>5.2</v>
       </c>
       <c r="N50" t="n">
-        <v>1.55</v>
+        <v>11</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="P50" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.57</v>
+        <v>4.5</v>
       </c>
       <c r="R50" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S50" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="T50" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="U50" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="V50" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="W50" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X50" t="n">
         <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH50" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.19</v>
+        <v>3.55</v>
       </c>
       <c r="M51" t="n">
-        <v>5.2</v>
+        <v>3.36</v>
       </c>
       <c r="N51" t="n">
-        <v>11</v>
+        <v>1.85</v>
       </c>
       <c r="O51" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="P51" t="n">
         <v>10</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="R51" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S51" t="n">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="T51" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="U51" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V51" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="W51" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X51" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y51" t="n">
         <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA51" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH51" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="M53" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N53" t="n">
-        <v>3.01</v>
+        <v>2.6</v>
       </c>
       <c r="O53" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="P53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="R53" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="S53" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="T53" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X53" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y53" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.91</v>
+        <v>3.94</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AH53" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="AI53" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N58" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="O58" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P58" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R58" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S58" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="T58" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V58" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="W58" t="n">
         <v>1.06</v>
       </c>
       <c r="X58" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AE58" t="n">
         <v>1.22</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH58" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,76 +8198,76 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P60" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q60" t="n">
         <v>2.3</v>
       </c>
-      <c r="M60" t="n">
+      <c r="R60" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T60" t="n">
         <v>3.1</v>
       </c>
-      <c r="N60" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P60" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3.14</v>
-      </c>
       <c r="U60" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V60" t="n">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W60" t="n">
         <v>1.06</v>
       </c>
       <c r="X60" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD60" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AE60" t="n">
         <v>1.22</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH60" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,76 +8462,76 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,61 +8990,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="M65" t="n">
-        <v>3.36</v>
+        <v>3.51</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O65" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="P65" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R65" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S65" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="T65" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U65" t="n">
         <v>1.4</v>
       </c>
       <c r="V65" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="W65" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X65" t="n">
         <v>1.06</v>
       </c>
-      <c r="X65" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y65" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AE65" t="n">
         <v>1.3</v>
@@ -9053,13 +9053,13 @@
         <v>1.77</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH65" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,28 +9122,28 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="M66" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="N66" t="n">
-        <v>2.31</v>
+        <v>2.51</v>
       </c>
       <c r="O66" t="n">
         <v>2.05</v>
       </c>
       <c r="P66" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R66" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S66" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="T66" t="n">
         <v>3</v>
@@ -9152,31 +9152,31 @@
         <v>1.33</v>
       </c>
       <c r="V66" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W66" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X66" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y66" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AA66" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AD66" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AE66" t="n">
         <v>1.22</v>
@@ -9185,7 +9185,7 @@
         <v>1.83</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH66" t="n">
         <v>8</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,76 +9254,76 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="M67" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.18</v>
+        <v>2.46</v>
       </c>
       <c r="O67" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="R67" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V67" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z67" t="n">
         <v>1.22</v>
       </c>
-      <c r="S67" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V67" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA67" t="n">
-        <v>5.15</v>
+        <v>3.9</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AD67" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>3.45</v>
+        <v>5.05</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,76 +9386,76 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="M68" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="N68" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="P68" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="R68" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S68" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="T68" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="U68" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V68" t="n">
-        <v>5.85</v>
+        <v>6.3</v>
       </c>
       <c r="W68" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X68" t="n">
         <v>1.05</v>
       </c>
       <c r="Y68" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AH68" t="n">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M69" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="O69" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,76 +9650,76 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M70" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="O70" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P70" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V70" t="n">
+        <v>8</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB70" t="n">
         <v>1.93</v>
       </c>
-      <c r="P70" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>2</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S70" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V70" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X70" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC70" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH70" t="n">
-        <v>5.15</v>
+        <v>7</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,73 +9782,73 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="M71" t="n">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="N71" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="O71" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="P71" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q71" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V71" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG71" t="n">
         <v>1.85</v>
       </c>
-      <c r="R71" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S71" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T71" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V71" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W71" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X71" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AH71" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AI71" t="n">
         <v>1.07</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,76 +9914,76 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="M72" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N72" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="O72" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="P72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q72" t="n">
+        <v>2</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T72" t="n">
         <v>2.5</v>
       </c>
-      <c r="R72" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S72" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U72" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="V72" t="n">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="W72" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y72" t="n">
-        <v>14.2</v>
+        <v>11.5</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AA72" t="n">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH72" t="n">
-        <v>3.96</v>
+        <v>5.15</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,76 +10178,76 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="M74" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>2.99</v>
+        <v>2.25</v>
       </c>
       <c r="O74" t="n">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="P74" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="R74" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S74" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="T74" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U74" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V74" t="n">
-        <v>8</v>
+        <v>6.45</v>
       </c>
       <c r="W74" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X74" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y74" t="n">
         <v>9</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AA74" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD74" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AE74" t="n">
         <v>1.28</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AH74" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,76 +10310,76 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N75" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,76 +10442,76 @@
         </is>
       </c>
       <c r="L76" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P76" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U76" t="n">
         <v>1.67</v>
       </c>
-      <c r="M76" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N76" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P76" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q76" t="n">
+      <c r="V76" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC76" t="n">
         <v>2.7</v>
       </c>
-      <c r="R76" t="n">
+      <c r="AD76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF76" t="n">
         <v>1.4</v>
       </c>
-      <c r="S76" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T76" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V76" t="n">
-        <v>7</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X76" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG76" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="AH76" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="M78" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N78" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="P78" t="n">
         <v>11</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R78" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S78" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T78" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U78" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="V78" t="n">
-        <v>4.45</v>
+        <v>5.05</v>
       </c>
       <c r="W78" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X78" t="n">
         <v>1.01</v>
       </c>
       <c r="Y78" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA78" t="n">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH78" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,76 +10970,76 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.63</v>
+        <v>11</v>
       </c>
       <c r="M80" t="n">
-        <v>2.93</v>
+        <v>6.5</v>
       </c>
       <c r="N80" t="n">
-        <v>2.51</v>
+        <v>1.18</v>
       </c>
       <c r="O80" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T80" t="n">
         <v>2.05</v>
       </c>
-      <c r="P80" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q80" t="n">
+      <c r="U80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V80" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD80" t="n">
         <v>2.1</v>
       </c>
-      <c r="R80" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S80" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T80" t="n">
-        <v>3</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V80" t="n">
-        <v>8</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X80" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AE80" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AH80" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,76 +11102,76 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N81" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC81" t="n">
         <v>1.91</v>
       </c>
-      <c r="P81" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R81" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S81" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V81" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W81" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X81" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AD81" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,76 +11234,76 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="M82" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="O82" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="P82" t="n">
-        <v>16.25</v>
+        <v>7.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="R82" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S82" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="T82" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="U82" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="V82" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="W82" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X82" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y82" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AA82" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.6</v>
+        <v>2.21</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.5</v>
+        <v>3.84</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG82" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="AH82" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="M83" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="M85" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N85" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="O85" t="n">
         <v>1.85</v>
@@ -11648,55 +11648,55 @@
         <v>2.25</v>
       </c>
       <c r="R85" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S85" t="n">
         <v>3.03</v>
       </c>
       <c r="T85" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U85" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V85" t="n">
         <v>5.8</v>
       </c>
       <c r="W85" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X85" t="n">
         <v>1.01</v>
       </c>
       <c r="Y85" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AA85" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD85" t="n">
         <v>3.15</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF85" t="n">
         <v>1.65</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="n">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="AI85" t="n">
         <v>1.11</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>10.05</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="M87" t="n">
-        <v>6.26</v>
+        <v>3.25</v>
       </c>
       <c r="N87" t="n">
-        <v>10.05</v>
+        <v>4</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,16 +11942,16 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="AD87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,73 +12158,73 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.46</v>
+        <v>3.41</v>
       </c>
       <c r="M89" t="n">
-        <v>3.21</v>
+        <v>3.68</v>
       </c>
       <c r="N89" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R89" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S89" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T89" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U89" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V89" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W89" t="n">
         <v>1.13</v>
       </c>
       <c r="X89" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA89" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC89" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AI89" t="n">
         <v>1.12</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.64</v>
+        <v>2.38</v>
       </c>
       <c r="M90" t="n">
-        <v>3.57</v>
+        <v>3.37</v>
       </c>
       <c r="N90" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="O90" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S90" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="T90" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U90" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V90" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W90" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AI90" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X90" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE90" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI90" t="n">
-        <v>1.18</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12418,80 +12418,80 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.68</v>
+        <v>3.64</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="N91" t="n">
-        <v>4.7</v>
+        <v>1.77</v>
       </c>
       <c r="O91" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R91" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S91" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="T91" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U91" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V91" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W91" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X91" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AA91" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB91" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AD91" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AF91" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG91" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AH91" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12682,80 +12682,80 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="M93" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N93" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S93" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T93" t="n">
         <v>3</v>
       </c>
-      <c r="O93" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R93" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S93" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T93" t="n">
-        <v>2.93</v>
-      </c>
       <c r="U93" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V93" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W93" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X93" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AI93" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X93" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF93" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG93" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,76 +12818,76 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.41</v>
+        <v>2.1</v>
       </c>
       <c r="M94" t="n">
-        <v>3.68</v>
+        <v>3.39</v>
       </c>
       <c r="N94" t="n">
-        <v>1.98</v>
+        <v>2.87</v>
       </c>
       <c r="O94" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="P94" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="R94" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S94" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T94" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="U94" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="V94" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="W94" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X94" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI94" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>1.12</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,76 +12950,76 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI95" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,76 +13082,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="M96" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N96" t="n">
+        <v>8</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P96" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q96" t="n">
         <v>3.25</v>
       </c>
-      <c r="O96" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P96" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R96" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S96" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="T96" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="V96" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="W96" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X96" t="n">
         <v>1.01</v>
       </c>
       <c r="Y96" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AA96" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH96" t="n">
-        <v>5.2</v>
+        <v>3.22</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,76 +13214,76 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>3.02</v>
       </c>
       <c r="AB98" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC98" t="n">
         <v>1.7</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,76 +13742,76 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,76 +13874,76 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,76 +14138,76 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="M104" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>3.5</v>
+        <v>4.21</v>
       </c>
       <c r="O104" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S104" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="T104" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U104" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V104" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="W104" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X104" t="n">
         <v>1.05</v>
       </c>
       <c r="Y104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AD104" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF104" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG104" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH104" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AI104" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14552,58 +14552,58 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,76 +14666,76 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI108" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>

--- a/jogos_2025-08-15.xlsx
+++ b/jogos_2025-08-15.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="N4" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="O4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.65</v>
       </c>
-      <c r="P4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,73 +1070,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="N5" t="n">
-        <v>2.57</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
         <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.38</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI5" t="n">
         <v>1.08</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,52 +1202,52 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.23</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.95</v>
       </c>
-      <c r="P6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
         <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>6.75</v>
+        <v>7.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
         <v>2.17</v>
@@ -1256,22 +1256,22 @@
         <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,64 +1334,64 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.78</v>
+        <v>3.69</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
         <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
         <v>1.83</v>
@@ -1400,10 +1400,10 @@
         <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="P20" t="n">
-        <v>6.15</v>
+        <v>17.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="V20" t="n">
-        <v>9.85</v>
+        <v>5.45</v>
       </c>
       <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y20" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.39</v>
+        <v>4.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>2.51</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.23</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="N22" t="n">
-        <v>2.35</v>
+        <v>3.12</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>9.85</v>
       </c>
       <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.1</v>
       </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,40 +3446,40 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3506,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="N30" t="n">
-        <v>1.91</v>
+        <v>3.03</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>5.2</v>
+        <v>5.85</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="M32" t="n">
-        <v>5.5</v>
+        <v>3.92</v>
       </c>
       <c r="N32" t="n">
-        <v>11.5</v>
+        <v>3.78</v>
       </c>
       <c r="O32" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="P32" t="n">
-        <v>13.75</v>
+        <v>9</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
         <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="U32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.57</v>
       </c>
-      <c r="V32" t="n">
-        <v>5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="O33" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V33" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
         <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>3.02</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>2.21</v>
       </c>
       <c r="O34" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="P34" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="T34" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.62</v>
       </c>
-      <c r="V34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG34" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,37 +5426,37 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="N38" t="n">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="O38" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="P38" t="n">
-        <v>9</v>
+        <v>18.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T38" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="V38" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W38" t="n">
         <v>1.14</v>
@@ -5465,37 +5465,37 @@
         <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>13.4</v>
+        <v>14.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.54</v>
+        <v>5.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AH38" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="M40" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="N40" t="n">
-        <v>3.03</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="P40" t="n">
         <v>10</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="R40" t="n">
         <v>1.32</v>
       </c>
       <c r="S40" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="U40" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V40" t="n">
-        <v>5.85</v>
+        <v>5.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>5.3</v>
+        <v>4.73</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U41" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="O42" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="P42" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="W42" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AH42" t="n">
-        <v>4.47</v>
+        <v>4.7</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="O43" t="n">
         <v>2.15</v>
@@ -6104,7 +6104,7 @@
         <v>1.72</v>
       </c>
       <c r="R43" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
         <v>3.04</v>
@@ -6119,7 +6119,7 @@
         <v>5.8</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
         <v>1.04</v>
@@ -6134,7 +6134,7 @@
         <v>3.7</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -6146,7 +6146,7 @@
         <v>1.38</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG43" t="n">
         <v>2.2</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O46" t="n">
         <v>2.3</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.83</v>
-      </c>
       <c r="P46" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="U46" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="V46" t="n">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AB46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG46" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC46" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH46" t="n">
-        <v>7.1</v>
+        <v>5.75</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M47" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="P47" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q47" t="n">
         <v>2.2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="W47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AI47" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.1</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="M48" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="N48" t="n">
-        <v>1.55</v>
+        <v>2.79</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="P48" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="R48" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T48" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V48" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="W48" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="Z48" t="n">
         <v>1.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6.3</v>
+        <v>1.19</v>
       </c>
       <c r="M49" t="n">
         <v>5.2</v>
       </c>
       <c r="N49" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="O49" t="n">
-        <v>3.32</v>
+        <v>1.25</v>
       </c>
       <c r="P49" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.32</v>
+        <v>4.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="S49" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="T49" t="n">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="U49" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="V49" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="W49" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AA49" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.39</v>
+        <v>1.55</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.19</v>
+        <v>5.4</v>
       </c>
       <c r="M50" t="n">
-        <v>5.2</v>
+        <v>3.41</v>
       </c>
       <c r="N50" t="n">
-        <v>11</v>
+        <v>1.55</v>
       </c>
       <c r="O50" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.5</v>
+        <v>1.57</v>
       </c>
       <c r="R50" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S50" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="T50" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="U50" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="V50" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="W50" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
         <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH50" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.55</v>
+        <v>6.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.36</v>
+        <v>5.2</v>
       </c>
       <c r="N51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P51" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T51" t="n">
         <v>1.85</v>
       </c>
-      <c r="O51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U51" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="V51" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X51" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.8</v>
+        <v>7.1</v>
       </c>
       <c r="AB51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AE51" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF51" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH51" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,76 +8198,76 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="O60" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="P60" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R60" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S60" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="T60" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U60" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V60" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W60" t="n">
-        <v>1.06</v